--- a/examples/programacion_malvinas.xlsx
+++ b/examples/programacion_malvinas.xlsx
@@ -483,11 +483,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7778.44</v>
+        <v>9249.629999999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02H43</t>
+          <t>03H14</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -512,11 +512,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10818.83</v>
+        <v>13033.32</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>02H50</t>
+          <t>03H25</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -576,7 +576,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>00H36</t>
+          <t>00H45</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1729.41</v>
+        <v>2141.34</v>
       </c>
     </row>
     <row r="4">
@@ -802,7 +802,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24.1 km — vuelo estimado 00H06</t>
+          <t>24.1 km — vuelo estimado 00H07</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>09H06</t>
+          <t>09H07</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>38.4 km — vuelo estimado 00H10</t>
+          <t>38.4 km — vuelo estimado 00H11</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>09H15</t>
+          <t>09H18</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10.8 km — vuelo estimado 00H03</t>
+          <t>10.8 km — vuelo estimado 00H04</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>09H18</t>
+          <t>09H22</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9.9 km — vuelo estimado 00H02</t>
+          <t>9.9 km — vuelo estimado 00H04</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>09H20</t>
+          <t>09H25</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>09H20</t>
+          <t>09H25</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9.9 km — vuelo estimado 00H02</t>
+          <t>9.9 km — vuelo estimado 00H04</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>09H23</t>
+          <t>09H29</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>25.1 km — vuelo estimado 00H06</t>
+          <t>25.1 km — vuelo estimado 00H08</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>09H29</t>
+          <t>09H36</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>27.0 km — vuelo estimado 00H07</t>
+          <t>27.0 km — vuelo estimado 00H08</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>09H36</t>
+          <t>09H44</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>09H36</t>
+          <t>09H44</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>09H36</t>
+          <t>09H44</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>09H36</t>
+          <t>09H44</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>09H36</t>
+          <t>09H44</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hora estimada: 09H36</t>
+          <t>Hora estimada: 09H44</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>00H15</t>
+          <t>00H17</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>715</v>
+        <v>832.7</v>
       </c>
     </row>
     <row r="32">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>30.0 km — vuelo estimado 00H08</t>
+          <t>30.0 km — vuelo estimado 00H09</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>09H43</t>
+          <t>09H53</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>30.0 km — vuelo estimado 00H08</t>
+          <t>30.0 km — vuelo estimado 00H09</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>09H51</t>
+          <t>10H02</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hora estimada: 09H51</t>
+          <t>Hora estimada: 10H02</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>00H22</t>
+          <t>00H26</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1065.08</v>
+        <v>1241.62</v>
       </c>
     </row>
     <row r="42">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>31.3 km — vuelo estimado 00H08</t>
+          <t>31.3 km — vuelo estimado 00H09</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>09H59</t>
+          <t>10H11</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>13.4 km — vuelo estimado 00H03</t>
+          <t>13.4 km — vuelo estimado 00H05</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>10H02</t>
+          <t>10H16</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>44.7 km — vuelo estimado 00H11</t>
+          <t>44.7 km — vuelo estimado 00H12</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>10H13</t>
+          <t>10H28</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hora estimada: 10H13</t>
+          <t>Hora estimada: 10H28</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>00H20</t>
+          <t>00H24</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>956.51</v>
+        <v>1133.06</v>
       </c>
     </row>
     <row r="54">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>23.0 km — vuelo estimado 00H06</t>
+          <t>23.0 km — vuelo estimado 00H07</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>10H19</t>
+          <t>10H35</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30.3 km — vuelo estimado 00H08</t>
+          <t>30.3 km — vuelo estimado 00H09</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>10H26</t>
+          <t>10H44</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>27.0 km — vuelo estimado 00H07</t>
+          <t>27.0 km — vuelo estimado 00H08</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>10H33</t>
+          <t>10H52</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Hora estimada: 10H33</t>
+          <t>Hora estimada: 10H52</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>00H22</t>
+          <t>00H26</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1070.49</v>
+        <v>1247.04</v>
       </c>
     </row>
     <row r="66">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>32.7 km — vuelo estimado 00H08</t>
+          <t>32.7 km — vuelo estimado 00H09</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>10H41</t>
+          <t>11H01</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30.1 km — vuelo estimado 00H08</t>
+          <t>30.1 km — vuelo estimado 00H09</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>10H49</t>
+          <t>11H10</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>27.0 km — vuelo estimado 00H07</t>
+          <t>27.0 km — vuelo estimado 00H08</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>10H56</t>
+          <t>11H18</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>10H56</t>
+          <t>11H18</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hora estimada: 10H56</t>
+          <t>Hora estimada: 11H18</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>00H19</t>
+          <t>00H23</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>920.29</v>
+        <v>1096.83</v>
       </c>
     </row>
     <row r="79">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>27.0 km — vuelo estimado 00H07</t>
+          <t>27.0 km — vuelo estimado 00H08</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>11H02</t>
+          <t>11H26</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>16.2 km — vuelo estimado 00H04</t>
+          <t>16.2 km — vuelo estimado 00H05</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>11H06</t>
+          <t>11H31</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>34.0 km — vuelo estimado 00H08</t>
+          <t>34.0 km — vuelo estimado 00H10</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>11H15</t>
+          <t>11H41</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>11H15</t>
+          <t>11H41</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Hora estimada: 11H15</t>
+          <t>Hora estimada: 11H41</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>00H12</t>
+          <t>00H15</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>574.75</v>
+        <v>692.4400000000001</v>
       </c>
     </row>
     <row r="92">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>24.1 km — vuelo estimado 00H06</t>
+          <t>24.1 km — vuelo estimado 00H07</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>11H21</t>
+          <t>11H48</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>24.1 km — vuelo estimado 00H06</t>
+          <t>24.1 km — vuelo estimado 00H07</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>11H27</t>
+          <t>11H55</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Hora estimada: 11H27</t>
+          <t>Hora estimada: 11H55</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>00H16</t>
+          <t>00H18</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>746.92</v>
+        <v>864.61</v>
       </c>
     </row>
     <row r="102">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>31.3 km — vuelo estimado 00H08</t>
+          <t>31.3 km — vuelo estimado 00H09</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>11H35</t>
+          <t>12H04</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>11H35</t>
+          <t>12H04</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>31.3 km — vuelo estimado 00H08</t>
+          <t>31.3 km — vuelo estimado 00H09</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>11H43</t>
+          <t>12H14</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Hora estimada: 11H43</t>
+          <t>Hora estimada: 12H14</t>
         </is>
       </c>
     </row>

--- a/examples/programacion_malvinas.xlsx
+++ b/examples/programacion_malvinas.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Programación" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Requerimientos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Tiempo en tierra" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Requerimientos" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -553,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K108"/>
+  <dimension ref="A1:K134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,192 +796,151 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>De MALV a MIPA</t>
-        </is>
-      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24.1 km — vuelo estimado 00H07</t>
+          <t>En tierra 26.9 min (admisible 6 min; exceso 20.9 min → cargo al cliente 907.40)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MALV</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P04/2</t>
+          <t>De MALV a MIPA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>MIPA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>ORIG: MALV</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>PAX</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>100</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>09H07</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Relevo</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Empresa B</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Camisea</t>
+          <t>24.1 km — vuelo estimado 00H07</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>De MIPA a SMK3</t>
+          <t>P04/2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>38.4 km — vuelo estimado 00H11</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MIPA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ORIG: MALV</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PAX</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>100</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>09H34</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Relevo</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Empresa B</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Camisea</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>P16/2</t>
-        </is>
-      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>En tierra 4.5 min</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SMK3</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>DEST: MALV</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CARGA</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>200</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>09H18</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Muestras y equipos</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Empresa B</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Camisea</t>
+          <t>MIPA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>De SMK3 a SM03</t>
+          <t>De MIPA a SMK3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10.8 km — vuelo estimado 00H04</t>
+          <t>38.4 km — vuelo estimado 00H11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P16/2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SM03</t>
+          <t>SMK3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ORIG: MALV</t>
+          <t>DEST: MALV</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PAX</t>
+          <t>CARGA</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>09H22</t>
+          <t>09H49</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Relevo</t>
+          <t>Muestras y equipos</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Empresa A</t>
+          <t>Empresa B</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -990,77 +950,48 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>De SM03 a SM01</t>
-        </is>
-      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9.9 km — vuelo estimado 00H04</t>
+          <t>En tierra 6.0 min</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SMK3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VIP1#1</t>
+          <t>De SMK3 a SM03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>SM01</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>ORIG: MALV</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>PAX</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>97</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>09H25</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>10.8 km — vuelo estimado 00H04</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VIP1#2</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SM01</t>
+          <t>SM03</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DEST: SM03</t>
+          <t>ORIG: MALV</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1069,89 +1000,101 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>97</v>
+        <v>800</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>09H25</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>09H59</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Relevo</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Empresa A</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Camisea</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>De SM01 a SM03</t>
-        </is>
-      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9.9 km — vuelo estimado 00H04</t>
+          <t>En tierra 22.0 min (admisible 6 min; exceso 16.0 min → cargo al cliente 693.33)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SM03</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>VIP1#2</t>
+          <t>De SM03 a SM01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>SM03</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>ORIG: SM01</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>PAX</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>97</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>09H29</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>9.9 km — vuelo estimado 00H04</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>De SM03 a PAGA</t>
+          <t>VIP1#1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>25.1 km — vuelo estimado 00H08</t>
-        </is>
-      </c>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SM01</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ORIG: MALV</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>PAX</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>97</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>10H25</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P13/2</t>
+          <t>VIP1#2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1161,115 +1104,62 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PAGA</t>
+          <t>SM01</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DEST: MALV</t>
+          <t>DEST: SM03</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CARGA</t>
+          <t>PAX</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>500</v>
+        <v>97</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>09H36</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Retorno de equipos</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Empresa C</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Camisea</t>
-        </is>
-      </c>
+          <t>10H25</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>De PAGA a MALV</t>
-        </is>
-      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>27.0 km — vuelo estimado 00H08</t>
+          <t>En tierra 6.9 min (admisible 6 min; exceso 0.9 min → cargo al cliente 38.13)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SM01</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P16/2</t>
+          <t>De SM01 a SM03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>MALV</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>ORIG: SMK3</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>CARGA</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22" t="n">
-        <v>200</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>09H44</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Muestras y equipos</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Empresa B</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Camisea</t>
+          <t>9.9 km — vuelo estimado 00H04</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P13/2</t>
+          <t>VIP1#2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1279,156 +1169,62 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MALV</t>
+          <t>SM03</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ORIG: PAGA</t>
+          <t>ORIG: SM01</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CARGA</t>
+          <t>PAX</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>500</v>
+        <v>97</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>09H44</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Retorno de equipos</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Empresa C</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Camisea</t>
-        </is>
-      </c>
+          <t>10H35</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>P07</t>
-        </is>
-      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>En tierra 4.4 min</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MALV</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>DEST: SM01</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>PAX</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>4</v>
-      </c>
-      <c r="G24" t="n">
-        <v>400</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>09H44</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Empresa C</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Camisea</t>
+          <t>SM03</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>De SM03 a PAGA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>MALV</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>DEST: MI24</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>PAX</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>3</v>
-      </c>
-      <c r="G25" t="n">
-        <v>300</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>09H44</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Supervisores</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Empresa A</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Camisea</t>
+          <t>25.1 km — vuelo estimado 00H08</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>P13/2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1438,831 +1234,882 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>PAGA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>DEST: MALV</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>CARGA</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>500</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>10H47</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Retorno de equipos</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Empresa C</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Camisea</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>En tierra 12.0 min (admisible 6 min; exceso 6.0 min → cargo al cliente 260.00)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PAGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>De PAGA a MALV</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>27.0 km — vuelo estimado 00H08</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>P16/2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>MALV</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>DEST: CAS3</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ORIG: SMK3</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>CARGA</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>200</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>11H07</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Muestras y equipos</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Empresa B</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Camisea</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>P13/2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ORIG: PAGA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>CARGA</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>500</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>11H07</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Retorno de equipos</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Empresa C</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Camisea</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>DEST: SM01</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>PAX</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="F31" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" t="n">
+        <v>400</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>11H07</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Empresa C</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Camisea</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>DEST: MI24</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PAX</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>3</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G32" t="n">
         <v>300</v>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>09H44</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>11H07</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Supervisores</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>Empresa A</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>Camisea</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Fin de rotación en MALV</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Hora estimada: 09H44</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>Helicóptero:</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Airbus H145 (OB2145)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>Tiempo horómetro:</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>00H17</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>Costo:</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>832.7</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>Req.</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>E/D</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>Ubic.</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="inlineStr">
-        <is>
-          <t>Dest/Orig</t>
-        </is>
-      </c>
-      <c r="E32" s="1" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="F32" s="1" t="inlineStr">
-        <is>
-          <t>#U</t>
-        </is>
-      </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>Total kg</t>
-        </is>
-      </c>
-      <c r="H32" s="1" t="inlineStr">
-        <is>
-          <t>Hora</t>
-        </is>
-      </c>
-      <c r="I32" s="1" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="J32" s="1" t="inlineStr">
-        <is>
-          <t>Empresa</t>
-        </is>
-      </c>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>Proyecto</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>De MALV a SM01</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>30.0 km — vuelo estimado 00H09</t>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>DEST: CAS3</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PAX</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" t="n">
+        <v>300</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>11H07</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Empresa A</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Camisea</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>P07</t>
-        </is>
-      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>En tierra 41.0 min (admisible 6 min; exceso 35.0 min → cargo al cliente 1516.67)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SM01</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>ORIG: MALV</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>PAX</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>4</v>
-      </c>
-      <c r="G34" t="n">
-        <v>400</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>09H53</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Empresa C</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Camisea</t>
+          <t>MALV</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>De SM01 a MALV</t>
+          <t>Fin de rotación en MALV</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>30.0 km — vuelo estimado 00H09</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>P01/2</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>MALV</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>DEST: CAS1</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>PAX</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>2</v>
-      </c>
-      <c r="G36" t="n">
-        <v>200</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>10H02</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Relevo de cuadrilla</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Empresa A</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Camisea</t>
+          <t>Hora estimada: 11H07</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Fin de rotación en MALV</t>
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Helicóptero:</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hora estimada: 10H02</t>
+          <t>Airbus H145 (OB2145)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Tiempo horómetro:</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>00H17</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Helicóptero:</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Airbus H145 (OB2145)</t>
-        </is>
+          <t>Costo:</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>832.7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Tiempo horómetro:</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>00H26</t>
+          <t>Req.</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>E/D</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>Ubic.</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>Dest/Orig</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="F40" s="1" t="inlineStr">
+        <is>
+          <t>#U</t>
+        </is>
+      </c>
+      <c r="G40" s="1" t="inlineStr">
+        <is>
+          <t>Total kg</t>
+        </is>
+      </c>
+      <c r="H40" s="1" t="inlineStr">
+        <is>
+          <t>Hora</t>
+        </is>
+      </c>
+      <c r="I40" s="1" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="J40" s="1" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="K40" s="1" t="inlineStr">
+        <is>
+          <t>Proyecto</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>Costo:</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1241.62</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>De MALV a SM01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>30.0 km — vuelo estimado 00H09</t>
+        </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>Req.</t>
-        </is>
-      </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>E/D</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>Ubic.</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>Dest/Orig</t>
-        </is>
-      </c>
-      <c r="E42" s="1" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="F42" s="1" t="inlineStr">
-        <is>
-          <t>#U</t>
-        </is>
-      </c>
-      <c r="G42" s="1" t="inlineStr">
-        <is>
-          <t>Total kg</t>
-        </is>
-      </c>
-      <c r="H42" s="1" t="inlineStr">
-        <is>
-          <t>Hora</t>
-        </is>
-      </c>
-      <c r="I42" s="1" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="J42" s="1" t="inlineStr">
-        <is>
-          <t>Empresa</t>
-        </is>
-      </c>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>Proyecto</t>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SM01</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ORIG: MALV</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PAX</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>4</v>
+      </c>
+      <c r="G42" t="n">
+        <v>400</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>11H57</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Empresa C</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Camisea</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>De MALV a CAS1</t>
-        </is>
-      </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>31.3 km — vuelo estimado 00H09</t>
+          <t>En tierra 12.0 min (admisible 6 min; exceso 6.0 min → cargo al cliente 260.00)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SM01</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>P01/2</t>
+          <t>De SM01 a MALV</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CAS1</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>ORIG: MALV</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>PAX</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>2</v>
-      </c>
-      <c r="G44" t="n">
-        <v>200</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>10H11</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Relevo de cuadrilla</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Empresa A</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Camisea</t>
+          <t>30.0 km — vuelo estimado 00H09</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>De CAS1 a CAS3</t>
+          <t>P01/2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>13.4 km — vuelo estimado 00H05</t>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DEST: CAS1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PAX</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>200</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>12H18</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Relevo de cuadrilla</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Empresa A</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Camisea</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>P02</t>
-        </is>
-      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>En tierra 7.0 min (admisible 6 min; exceso 1.0 min → cargo al cliente 43.33)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CAS3</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>ORIG: MALV</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>PAX</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>3</v>
-      </c>
-      <c r="G46" t="n">
-        <v>300</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>10H16</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Empresa A</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Camisea</t>
+          <t>MALV</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>De CAS3 a MALV</t>
+          <t>Fin de rotación en MALV</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>44.7 km — vuelo estimado 00H12</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>MALV</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>DEST: CA19</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>PAX</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>6</v>
-      </c>
-      <c r="G48" t="n">
-        <v>600</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>10H28</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Operadores</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Empresa B</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Camisea</t>
+          <t>Hora estimada: 12H18</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Fin de rotación en MALV</t>
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>Helicóptero:</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hora estimada: 10H28</t>
+          <t>Airbus H145 (OB2145)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>Tiempo horómetro:</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>00H26</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>Helicóptero:</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Airbus H145 (OB2145)</t>
-        </is>
+          <t>Costo:</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1241.62</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>Tiempo horómetro:</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>00H24</t>
+          <t>Req.</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>E/D</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>Ubic.</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="inlineStr">
+        <is>
+          <t>Dest/Orig</t>
+        </is>
+      </c>
+      <c r="E52" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="F52" s="1" t="inlineStr">
+        <is>
+          <t>#U</t>
+        </is>
+      </c>
+      <c r="G52" s="1" t="inlineStr">
+        <is>
+          <t>Total kg</t>
+        </is>
+      </c>
+      <c r="H52" s="1" t="inlineStr">
+        <is>
+          <t>Hora</t>
+        </is>
+      </c>
+      <c r="I52" s="1" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="J52" s="1" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="K52" s="1" t="inlineStr">
+        <is>
+          <t>Proyecto</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>Costo:</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>1133.06</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>De MALV a CAS1</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>31.3 km — vuelo estimado 00H09</t>
+        </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>Req.</t>
-        </is>
-      </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>E/D</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>Ubic.</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>Dest/Orig</t>
-        </is>
-      </c>
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="F54" s="1" t="inlineStr">
-        <is>
-          <t>#U</t>
-        </is>
-      </c>
-      <c r="G54" s="1" t="inlineStr">
-        <is>
-          <t>Total kg</t>
-        </is>
-      </c>
-      <c r="H54" s="1" t="inlineStr">
-        <is>
-          <t>Hora</t>
-        </is>
-      </c>
-      <c r="I54" s="1" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="J54" s="1" t="inlineStr">
-        <is>
-          <t>Empresa</t>
-        </is>
-      </c>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>Proyecto</t>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>P01/2</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CAS1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ORIG: MALV</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>PAX</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G54" t="n">
+        <v>200</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>12H34</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Relevo de cuadrilla</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Empresa A</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Camisea</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>De MALV a CA19</t>
-        </is>
-      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>23.0 km — vuelo estimado 00H07</t>
+          <t>En tierra 7.0 min (admisible 6 min; exceso 1.0 min → cargo al cliente 43.33)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CAS1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>De CAS1 a CAS3</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>CA19</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>ORIG: MALV</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>PAX</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>6</v>
-      </c>
-      <c r="G56" t="n">
-        <v>600</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>10H35</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Operadores</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Empresa B</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Camisea</t>
+          <t>13.4 km — vuelo estimado 00H05</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>De CA19 a PAGA</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30.3 km — vuelo estimado 00H09</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>CAS3</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ORIG: MALV</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>PAX</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>3</v>
+      </c>
+      <c r="G57" t="n">
+        <v>300</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>12H45</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Empresa A</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Camisea</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>En tierra 9.5 min (admisible 6 min; exceso 3.5 min → cargo al cliente 151.67)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PAGA</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>DEST: MALV</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>PAX</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>7</v>
-      </c>
-      <c r="G58" t="n">
-        <v>700</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>10H44</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Bajada</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Empresa C</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>Camisea</t>
+          <t>CAS3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>De PAGA a MALV</t>
+          <t>De CAS3 a MALV</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>27.0 km — vuelo estimado 00H08</t>
+          <t>44.7 km — vuelo estimado 00H12</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2272,7 +2119,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ORIG: PAGA</t>
+          <t>DEST: CA19</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2281,24 +2128,24 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G60" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>10H52</t>
+          <t>13H07</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Bajada</t>
+          <t>Operadores</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Empresa C</t>
+          <t>Empresa B</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -2308,290 +2155,249 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>En tierra 17.0 min (admisible 6 min; exceso 11.0 min → cargo al cliente 476.67)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>Fin de rotación en MALV</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Hora estimada: 10H52</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="inlineStr">
-        <is>
-          <t>Helicóptero:</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Airbus H145 (OB2145)</t>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Hora estimada: 13H07</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>Tiempo horómetro:</t>
+          <t>Helicóptero:</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>00H26</t>
+          <t>Airbus H145 (OB2145)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>Costo:</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>1247.04</v>
+          <t>Tiempo horómetro:</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>00H24</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
+          <t>Costo:</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1133.06</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
           <t>Req.</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
+      <c r="B67" s="1" t="inlineStr">
         <is>
           <t>E/D</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>Ubic.</t>
         </is>
       </c>
-      <c r="D66" s="1" t="inlineStr">
+      <c r="D67" s="1" t="inlineStr">
         <is>
           <t>Dest/Orig</t>
         </is>
       </c>
-      <c r="E66" s="1" t="inlineStr">
+      <c r="E67" s="1" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="F66" s="1" t="inlineStr">
+      <c r="F67" s="1" t="inlineStr">
         <is>
           <t>#U</t>
         </is>
       </c>
-      <c r="G66" s="1" t="inlineStr">
+      <c r="G67" s="1" t="inlineStr">
         <is>
           <t>Total kg</t>
         </is>
       </c>
-      <c r="H66" s="1" t="inlineStr">
+      <c r="H67" s="1" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="I66" s="1" t="inlineStr">
+      <c r="I67" s="1" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="J66" s="1" t="inlineStr">
+      <c r="J67" s="1" t="inlineStr">
         <is>
           <t>Empresa</t>
         </is>
       </c>
-      <c r="K66" s="1" t="inlineStr">
+      <c r="K67" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>De MALV a MI24</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>32.7 km — vuelo estimado 00H09</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>De MALV a CA19</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>MI24</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>ORIG: MALV</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>PAX</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>3</v>
-      </c>
-      <c r="G68" t="n">
-        <v>300</v>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>11H01</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Supervisores</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>Empresa A</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Camisea</t>
+          <t>23.0 km — vuelo estimado 00H07</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>De MI24 a PAGA</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30.1 km — vuelo estimado 00H09</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CA19</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ORIG: MALV</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>PAX</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>6</v>
+      </c>
+      <c r="G69" t="n">
+        <v>600</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>13H31</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Operadores</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Empresa B</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Camisea</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>P13/1</t>
-        </is>
-      </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>En tierra 17.0 min (admisible 6 min; exceso 11.0 min → cargo al cliente 476.67)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PAGA</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>DEST: MALV</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>CARGA</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>11</v>
-      </c>
-      <c r="G70" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>11H10</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Retorno de equipos</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Empresa C</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Camisea</t>
+          <t>CA19</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>De PAGA a MALV</t>
+          <t>De CA19 a PAGA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>27.0 km — vuelo estimado 00H08</t>
+          <t>30.3 km — vuelo estimado 00H09</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>P13/1</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MALV</t>
+          <t>PAGA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ORIG: PAGA</t>
+          <t>DEST: MALV</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CARGA</t>
+          <t>PAX</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G72" t="n">
-        <v>1100</v>
+        <v>700</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>11H18</t>
+          <t>13H57</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Retorno de equipos</t>
+          <t>Bajada</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -2606,884 +2412,812 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>En tierra 19.5 min (admisible 6 min; exceso 13.5 min → cargo al cliente 585.00)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MALV</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>DEST: PAGA</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>PAX</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>9</v>
-      </c>
-      <c r="G73" t="n">
-        <v>900</v>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>11H18</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Cuadrilla</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>Empresa C</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Camisea</t>
+          <t>PAGA</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>De PAGA a MALV</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>27.0 km — vuelo estimado 00H08</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ORIG: PAGA</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>PAX</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>7</v>
+      </c>
+      <c r="G75" t="n">
+        <v>700</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>14H24</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Bajada</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Empresa C</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Camisea</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>En tierra 19.5 min (admisible 6 min; exceso 13.5 min → cargo al cliente 585.00)</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>Fin de rotación en MALV</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Hora estimada: 11H18</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="inlineStr">
-        <is>
-          <t>Helicóptero:</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Airbus H145 (OB2145)</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr">
-        <is>
-          <t>Tiempo horómetro:</t>
-        </is>
-      </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>00H23</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="inlineStr">
-        <is>
-          <t>Costo:</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>1096.83</v>
+          <t>Hora estimada: 14H24</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
+          <t>Helicóptero:</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Airbus H145 (OB2145)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>Tiempo horómetro:</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>00H26</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>Costo:</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1247.04</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
           <t>Req.</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
+      <c r="B82" s="1" t="inlineStr">
         <is>
           <t>E/D</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>Ubic.</t>
         </is>
       </c>
-      <c r="D79" s="1" t="inlineStr">
+      <c r="D82" s="1" t="inlineStr">
         <is>
           <t>Dest/Orig</t>
         </is>
       </c>
-      <c r="E79" s="1" t="inlineStr">
+      <c r="E82" s="1" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="F79" s="1" t="inlineStr">
+      <c r="F82" s="1" t="inlineStr">
         <is>
           <t>#U</t>
         </is>
       </c>
-      <c r="G79" s="1" t="inlineStr">
+      <c r="G82" s="1" t="inlineStr">
         <is>
           <t>Total kg</t>
         </is>
       </c>
-      <c r="H79" s="1" t="inlineStr">
+      <c r="H82" s="1" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="I79" s="1" t="inlineStr">
+      <c r="I82" s="1" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="J79" s="1" t="inlineStr">
+      <c r="J82" s="1" t="inlineStr">
         <is>
           <t>Empresa</t>
         </is>
       </c>
-      <c r="K79" s="1" t="inlineStr">
+      <c r="K82" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>De MALV a PAGA</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>27.0 km — vuelo estimado 00H08</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>PAGA</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>ORIG: MALV</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>PAX</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>9</v>
-      </c>
-      <c r="G81" t="n">
-        <v>900</v>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>11H26</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Cuadrilla</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Empresa C</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Camisea</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>De PAGA a SMK3</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>16.2 km — vuelo estimado 00H05</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>P16/1</t>
+          <t>De MALV a MI24</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>SMK3</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>DEST: MALV</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>CARGA</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>11</v>
-      </c>
-      <c r="G83" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>11H31</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Muestras y equipos</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>Empresa B</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>Camisea</t>
+          <t>32.7 km — vuelo estimado 00H09</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>De SMK3 a MALV</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>34.0 km — vuelo estimado 00H10</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>MI24</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ORIG: MALV</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>PAX</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>3</v>
+      </c>
+      <c r="G84" t="n">
+        <v>300</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>14H53</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Supervisores</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Empresa A</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Camisea</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>P16/1</t>
-        </is>
-      </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>En tierra 9.5 min (admisible 6 min; exceso 3.5 min → cargo al cliente 151.67)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MALV</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>ORIG: SMK3</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>CARGA</t>
-        </is>
-      </c>
-      <c r="F85" t="n">
-        <v>11</v>
-      </c>
-      <c r="G85" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>11H41</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Muestras y equipos</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>Empresa B</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Camisea</t>
+          <t>MI24</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>P04/1</t>
+          <t>De MI24 a PAGA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>MALV</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>DEST: MIPA</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>PAX</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
-        <v>10</v>
-      </c>
-      <c r="G86" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>11H41</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Relevo</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>Empresa B</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Camisea</t>
+          <t>30.1 km — vuelo estimado 00H09</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Fin de rotación en MALV</t>
+          <t>P13/1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Hora estimada: 11H41</t>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>PAGA</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>DEST: MALV</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>CARGA</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>11</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>15H12</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Retorno de equipos</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Empresa C</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Camisea</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>En tierra 24.0 min (admisible 6 min; exceso 18.0 min → cargo al cliente 780.00)</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>PAGA</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="inlineStr">
-        <is>
-          <t>Helicóptero:</t>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>De PAGA a MALV</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Airbus H145 (OB2145)</t>
+          <t>27.0 km — vuelo estimado 00H08</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="inlineStr">
-        <is>
-          <t>Tiempo horómetro:</t>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>P13/1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>00H15</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ORIG: PAGA</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>CARGA</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>11</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>15H44</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Retorno de equipos</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Empresa C</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Camisea</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="inlineStr">
-        <is>
-          <t>Costo:</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>692.4400000000001</v>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>DEST: PAGA</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>PAX</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>9</v>
+      </c>
+      <c r="G91" t="n">
+        <v>900</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>15H44</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Cuadrilla</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Empresa C</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Camisea</t>
+        </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="inlineStr">
-        <is>
-          <t>Req.</t>
-        </is>
-      </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>E/D</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>Ubic.</t>
-        </is>
-      </c>
-      <c r="D92" s="1" t="inlineStr">
-        <is>
-          <t>Dest/Orig</t>
-        </is>
-      </c>
-      <c r="E92" s="1" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="F92" s="1" t="inlineStr">
-        <is>
-          <t>#U</t>
-        </is>
-      </c>
-      <c r="G92" s="1" t="inlineStr">
-        <is>
-          <t>Total kg</t>
-        </is>
-      </c>
-      <c r="H92" s="1" t="inlineStr">
-        <is>
-          <t>Hora</t>
-        </is>
-      </c>
-      <c r="I92" s="1" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="J92" s="1" t="inlineStr">
-        <is>
-          <t>Empresa</t>
-        </is>
-      </c>
-      <c r="K92" s="1" t="inlineStr">
-        <is>
-          <t>Proyecto</t>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>En tierra 46.5 min (admisible 6 min; exceso 40.5 min → cargo al cliente 1755.00)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>MALV</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>De MALV a MIPA</t>
+          <t>Fin de rotación en MALV</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>24.1 km — vuelo estimado 00H07</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>P04/1</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
+          <t>Hora estimada: 15H44</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>Helicóptero:</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Airbus H145 (OB2145)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>Tiempo horómetro:</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>00H23</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>Costo:</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1096.83</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>Req.</t>
+        </is>
+      </c>
+      <c r="B98" s="1" t="inlineStr">
+        <is>
+          <t>E/D</t>
+        </is>
+      </c>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>Ubic.</t>
+        </is>
+      </c>
+      <c r="D98" s="1" t="inlineStr">
+        <is>
+          <t>Dest/Orig</t>
+        </is>
+      </c>
+      <c r="E98" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="F98" s="1" t="inlineStr">
+        <is>
+          <t>#U</t>
+        </is>
+      </c>
+      <c r="G98" s="1" t="inlineStr">
+        <is>
+          <t>Total kg</t>
+        </is>
+      </c>
+      <c r="H98" s="1" t="inlineStr">
+        <is>
+          <t>Hora</t>
+        </is>
+      </c>
+      <c r="I98" s="1" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="J98" s="1" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="K98" s="1" t="inlineStr">
+        <is>
+          <t>Proyecto</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>De MALV a PAGA</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>27.0 km — vuelo estimado 00H08</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>MIPA</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>PAGA</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
         <is>
           <t>ORIG: MALV</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>PAX</t>
         </is>
       </c>
-      <c r="F94" t="n">
-        <v>10</v>
-      </c>
-      <c r="G94" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>11H48</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Relevo</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>Empresa B</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
+      <c r="F100" t="n">
+        <v>9</v>
+      </c>
+      <c r="G100" t="n">
+        <v>900</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>16H38</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Cuadrilla</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Empresa C</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
         <is>
           <t>Camisea</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>De MIPA a MALV</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>24.1 km — vuelo estimado 00H07</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>P01/1</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>MALV</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>DEST: CAS1</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>PAX</t>
-        </is>
-      </c>
-      <c r="F96" t="n">
-        <v>10</v>
-      </c>
-      <c r="G96" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>11H55</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Relevo de cuadrilla</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>Empresa A</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Camisea</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Fin de rotación en MALV</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Hora estimada: 11H55</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="1" t="inlineStr">
-        <is>
-          <t>Helicóptero:</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Airbus H145 (OB2145)</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="1" t="inlineStr">
-        <is>
-          <t>Tiempo horómetro:</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>00H18</t>
-        </is>
-      </c>
-    </row>
     <row r="101">
-      <c r="A101" s="1" t="inlineStr">
-        <is>
-          <t>Costo:</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>864.61</v>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>En tierra 24.5 min (admisible 6 min; exceso 18.5 min → cargo al cliente 801.67)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>PAGA</t>
+        </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="inlineStr">
-        <is>
-          <t>Req.</t>
-        </is>
-      </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>E/D</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>Ubic.</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>Dest/Orig</t>
-        </is>
-      </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="F102" s="1" t="inlineStr">
-        <is>
-          <t>#U</t>
-        </is>
-      </c>
-      <c r="G102" s="1" t="inlineStr">
-        <is>
-          <t>Total kg</t>
-        </is>
-      </c>
-      <c r="H102" s="1" t="inlineStr">
-        <is>
-          <t>Hora</t>
-        </is>
-      </c>
-      <c r="I102" s="1" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="J102" s="1" t="inlineStr">
-        <is>
-          <t>Empresa</t>
-        </is>
-      </c>
-      <c r="K102" s="1" t="inlineStr">
-        <is>
-          <t>Proyecto</t>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>De PAGA a SMK3</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>16.2 km — vuelo estimado 00H05</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>De MALV a CAS1</t>
+          <t>P16/1</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>31.3 km — vuelo estimado 00H09</t>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>SMK3</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>DEST: MALV</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>CARGA</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>11</v>
+      </c>
+      <c r="G103" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>17H08</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Muestras y equipos</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Empresa B</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Camisea</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>P01/1</t>
-        </is>
-      </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>En tierra 24.0 min (admisible 6 min; exceso 18.0 min → cargo al cliente 780.00)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CAS1</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>ORIG: MALV</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>PAX</t>
-        </is>
-      </c>
-      <c r="F104" t="n">
-        <v>10</v>
-      </c>
-      <c r="G104" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>12H04</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>Relevo de cuadrilla</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>Empresa A</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>Camisea</t>
+          <t>SMK3</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>De SMK3 a MALV</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>CAS1</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>DEST: MALV</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>PAX</t>
-        </is>
-      </c>
-      <c r="F105" t="n">
-        <v>10</v>
-      </c>
-      <c r="G105" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>12H04</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>Bajada de cuadrilla</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>Empresa A</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>Camisea</t>
+          <t>34.0 km — vuelo estimado 00H10</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>De CAS1 a MALV</t>
+          <t>P16/1</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>31.3 km — vuelo estimado 00H09</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ORIG: SMK3</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>CARGA</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>11</v>
+      </c>
+      <c r="G106" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>17H42</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Muestras y equipos</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Empresa B</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Camisea</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P04/1</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3493,7 +3227,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ORIG: CAS1</t>
+          <t>DEST: MIPA</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3509,34 +3243,613 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>12H14</t>
+          <t>17H42</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
+          <t>Relevo</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Empresa B</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Camisea</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>En tierra 49.0 min (admisible 6 min; exceso 43.0 min → cargo al cliente 1863.33)</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Fin de rotación en MALV</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Hora estimada: 17H42</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>Helicóptero:</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Airbus H145 (OB2145)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>Tiempo horómetro:</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>00H15</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>Costo:</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>692.4400000000001</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>Req.</t>
+        </is>
+      </c>
+      <c r="B114" s="1" t="inlineStr">
+        <is>
+          <t>E/D</t>
+        </is>
+      </c>
+      <c r="C114" s="1" t="inlineStr">
+        <is>
+          <t>Ubic.</t>
+        </is>
+      </c>
+      <c r="D114" s="1" t="inlineStr">
+        <is>
+          <t>Dest/Orig</t>
+        </is>
+      </c>
+      <c r="E114" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="F114" s="1" t="inlineStr">
+        <is>
+          <t>#U</t>
+        </is>
+      </c>
+      <c r="G114" s="1" t="inlineStr">
+        <is>
+          <t>Total kg</t>
+        </is>
+      </c>
+      <c r="H114" s="1" t="inlineStr">
+        <is>
+          <t>Hora</t>
+        </is>
+      </c>
+      <c r="I114" s="1" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="J114" s="1" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="K114" s="1" t="inlineStr">
+        <is>
+          <t>Proyecto</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>De MALV a MIPA</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>24.1 km — vuelo estimado 00H07</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>P04/1</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>MIPA</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ORIG: MALV</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>PAX</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>10</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>18H38</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Relevo</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Empresa B</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Camisea</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>En tierra 27.0 min (admisible 6 min; exceso 21.0 min → cargo al cliente 910.00)</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>MIPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>De MIPA a MALV</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>24.1 km — vuelo estimado 00H07</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>P01/1</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>DEST: CAS1</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>PAX</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>10</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>19H12</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Relevo de cuadrilla</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Empresa A</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Camisea</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>En tierra 27.0 min (admisible 6 min; exceso 21.0 min → cargo al cliente 910.00)</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Fin de rotación en MALV</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Hora estimada: 19H12</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>Helicóptero:</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Airbus H145 (OB2145)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>Tiempo horómetro:</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>00H18</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>Costo:</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>864.61</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>Req.</t>
+        </is>
+      </c>
+      <c r="B126" s="1" t="inlineStr">
+        <is>
+          <t>E/D</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="inlineStr">
+        <is>
+          <t>Ubic.</t>
+        </is>
+      </c>
+      <c r="D126" s="1" t="inlineStr">
+        <is>
+          <t>Dest/Orig</t>
+        </is>
+      </c>
+      <c r="E126" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="F126" s="1" t="inlineStr">
+        <is>
+          <t>#U</t>
+        </is>
+      </c>
+      <c r="G126" s="1" t="inlineStr">
+        <is>
+          <t>Total kg</t>
+        </is>
+      </c>
+      <c r="H126" s="1" t="inlineStr">
+        <is>
+          <t>Hora</t>
+        </is>
+      </c>
+      <c r="I126" s="1" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="J126" s="1" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="K126" s="1" t="inlineStr">
+        <is>
+          <t>Proyecto</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>De MALV a CAS1</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>31.3 km — vuelo estimado 00H09</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>P01/1</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>CAS1</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>ORIG: MALV</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>PAX</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>10</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>19H48</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Relevo de cuadrilla</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Empresa A</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Camisea</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>CAS1</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>DEST: MALV</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>PAX</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>10</v>
+      </c>
+      <c r="G129" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>19H48</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
           <t>Bajada de cuadrilla</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
+      <c r="J129" t="inlineStr">
         <is>
           <t>Empresa A</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="K129" t="inlineStr">
         <is>
           <t>Camisea</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
+    <row r="130">
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>En tierra 52.0 min (admisible 6 min; exceso 46.0 min → cargo al cliente 1993.33)</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>CAS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>De CAS1 a MALV</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>31.3 km — vuelo estimado 00H09</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ORIG: CAS1</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>PAX</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>10</v>
+      </c>
+      <c r="G132" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>20H49</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Bajada de cuadrilla</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Empresa A</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Camisea</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>En tierra 27.0 min (admisible 6 min; exceso 21.0 min → cargo al cliente 910.00)</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
         <is>
           <t>Fin de rotación en MALV</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Hora estimada: 12H14</t>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Hora estimada: 20H49</t>
         </is>
       </c>
     </row>
@@ -3551,6 +3864,1120 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tiempo en tierra estimado — Airbus H145 (admisible 6 min/parada)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Punto</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Hora llegada</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Pax mov.</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Kg mov.</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Min en tierra</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>Exceso (min)</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>Cargo al cliente</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>Empresas</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>09H00</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>997</v>
+      </c>
+      <c r="F4" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>907.4</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Empresa A, Empresa B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MIPA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>09H34</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Empresa B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SMK3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>09H49</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>200</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Empresa B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SM03</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>09H59</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>800</v>
+      </c>
+      <c r="F7" t="n">
+        <v>22</v>
+      </c>
+      <c r="G7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" t="n">
+        <v>693.33</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Empresa A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SM01</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>10H25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>194</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>38.13</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SM03</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10H35</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>97</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PAGA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>10H47</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>500</v>
+      </c>
+      <c r="F10" t="n">
+        <v>12</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>260</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Empresa C</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>11H07</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F11" t="n">
+        <v>41</v>
+      </c>
+      <c r="G11" t="n">
+        <v>35</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1516.67</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Empresa A, Empresa B, Empresa C</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SM01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>11H57</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>400</v>
+      </c>
+      <c r="F12" t="n">
+        <v>12</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>260</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Empresa C</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>12H18</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>200</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Empresa A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CAS1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>12H34</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>200</v>
+      </c>
+      <c r="F14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Empresa A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CAS3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>12H45</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>300</v>
+      </c>
+      <c r="F15" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>151.67</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Empresa A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>13H07</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>600</v>
+      </c>
+      <c r="F16" t="n">
+        <v>17</v>
+      </c>
+      <c r="G16" t="n">
+        <v>11</v>
+      </c>
+      <c r="H16" t="n">
+        <v>476.67</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Empresa B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CA19</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>13H31</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>600</v>
+      </c>
+      <c r="F17" t="n">
+        <v>17</v>
+      </c>
+      <c r="G17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H17" t="n">
+        <v>476.67</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Empresa B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PAGA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>13H57</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>585</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Empresa C</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>14H24</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" t="n">
+        <v>700</v>
+      </c>
+      <c r="F19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>585</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Empresa C</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MI24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>14H53</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>300</v>
+      </c>
+      <c r="F20" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>151.67</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Empresa A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PAGA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>15H12</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F21" t="n">
+        <v>24</v>
+      </c>
+      <c r="G21" t="n">
+        <v>18</v>
+      </c>
+      <c r="H21" t="n">
+        <v>780</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Empresa C</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>15H44</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>9</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F22" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1755</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Empresa C</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PAGA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>16H38</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>9</v>
+      </c>
+      <c r="E23" t="n">
+        <v>900</v>
+      </c>
+      <c r="F23" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>801.67</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Empresa C</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SMK3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>17H08</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F24" t="n">
+        <v>24</v>
+      </c>
+      <c r="G24" t="n">
+        <v>18</v>
+      </c>
+      <c r="H24" t="n">
+        <v>780</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Empresa B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>17H42</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F25" t="n">
+        <v>49</v>
+      </c>
+      <c r="G25" t="n">
+        <v>43</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1863.33</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Empresa B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MIPA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>18H38</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F26" t="n">
+        <v>27</v>
+      </c>
+      <c r="G26" t="n">
+        <v>21</v>
+      </c>
+      <c r="H26" t="n">
+        <v>910</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Empresa B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>19H12</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F27" t="n">
+        <v>27</v>
+      </c>
+      <c r="G27" t="n">
+        <v>21</v>
+      </c>
+      <c r="H27" t="n">
+        <v>910</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Empresa A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CAS1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>19H48</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F28" t="n">
+        <v>52</v>
+      </c>
+      <c r="G28" t="n">
+        <v>46</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1993.33</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Empresa A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>20H49</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F29" t="n">
+        <v>27</v>
+      </c>
+      <c r="G29" t="n">
+        <v>21</v>
+      </c>
+      <c r="H29" t="n">
+        <v>910</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Empresa A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Resumen por empresa (cliente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>Mín (min)</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>Promedio (min)</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>Máx (min)</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>Exceso total (min)</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>Cargo extra total</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>(sin empresa)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G33" t="n">
+        <v>38.13</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Empresa A</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>10</v>
+      </c>
+      <c r="C34" t="n">
+        <v>7</v>
+      </c>
+      <c r="D34" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E34" t="n">
+        <v>52</v>
+      </c>
+      <c r="F34" t="n">
+        <v>168.9</v>
+      </c>
+      <c r="G34" t="n">
+        <v>7320.73</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Empresa B</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>9</v>
+      </c>
+      <c r="C35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D35" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E35" t="n">
+        <v>49</v>
+      </c>
+      <c r="F35" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="G35" t="n">
+        <v>6930.73</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Empresa C</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>8</v>
+      </c>
+      <c r="C36" t="n">
+        <v>12</v>
+      </c>
+      <c r="D36" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E36" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>151</v>
+      </c>
+      <c r="G36" t="n">
+        <v>6543.33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
